--- a/data/trans_orig/P16B13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,97 +845,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>42,86%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>869</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5112</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>43,29%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1531,97 +1531,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1898</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5096</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>43,34%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>42,95%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5054</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,97 +1874,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5215</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>976</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4279</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>20,47%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4005</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,97 +2217,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4793</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>940</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4769</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32067</t>
+          <t>33781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2560,97 +2560,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1811</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4575</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4605</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>17,97%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6038</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23227</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>34354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,62 +2938,62 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75049</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84577</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>108176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>117503</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>188423</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>200356</t>
+          <t>200197</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,42 +3731,42 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>91,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -3824,62 +3824,62 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5344</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>38,78%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1407</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,62 +4545,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1914</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5814</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31355</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57678</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68445</t>
+          <t>68447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5196,97 +5196,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59342</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61367</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5539,97 +5539,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2237</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>26237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68750</t>
+          <t>67745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,62 +5917,62 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>4947</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120219</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135496</t>
+          <t>134559</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>182076</t>
+          <t>182299</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189201</t>
+          <t>189197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>305713</t>
+          <t>306978</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>322735</t>
+          <t>322831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016 (tasa de respuesta: 97,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6803,97 +6803,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1674</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7181,62 +7181,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6861</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>7560</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7489,97 +7489,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5538</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>51,11%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>1809</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5848</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,62 +7867,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2797</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1855</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8155</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>8791</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>31686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54289</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36295</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8518,97 +8518,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5026</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>973</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5094</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56319</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58470</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8861,97 +8861,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84259</t>
+          <t>82754</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96038</t>
+          <t>96227</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129107</t>
+          <t>129934</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>137993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218352</t>
+          <t>218348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>232463</t>
+          <t>232777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P16B13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Edad-trans_orig.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>22537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27680</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32567</t>
+          <t>32729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34354</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>75807</t>
+          <t>75932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84582</t>
+          <t>84579</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>107718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117503</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>187776</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>200197</t>
+          <t>200566</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>34043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>30891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55138</t>
+          <t>57949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68447</t>
+          <t>68482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26273</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67745</t>
+          <t>68057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120219</t>
+          <t>119434</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134559</t>
+          <t>134738</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>182299</t>
+          <t>182112</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189197</t>
+          <t>189200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>306978</t>
+          <t>306537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>322831</t>
+          <t>322736</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20096</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31686</t>
+          <t>29958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>18979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36066</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82754</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96227</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129934</t>
+          <t>129597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137993</t>
+          <t>138012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218348</t>
+          <t>218329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>232777</t>
+          <t>232549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
